--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:45</t>
+    <t xml:space="preserve">2026-09-10 00:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:54</t>
+    <t xml:space="preserve">2026-09-18 11:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:03</t>
+    <t xml:space="preserve">2026-09-23 14:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:24</t>
+    <t xml:space="preserve">2026-10-02 15:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2020_biobio.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Concepción</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">San Rosendo</t>
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Curanilahue</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Quilleco</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:41</t>
+    <t xml:space="preserve">2026-10-04 10:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:09</t>
+    <t xml:space="preserve">2026-10-05 14:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
